--- a/volumes/02-solar-home-systems/decision-tools/AEF_V2_D3_Repayment_Curve_and_Calibration.xlsx
+++ b/volumes/02-solar-home-systems/decision-tools/AEF_V2_D3_Repayment_Curve_and_Calibration.xlsx
@@ -703,7 +703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D3  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D3  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -764,7 +764,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Draws the expected repayment curve of a cohort from a monthly default hazard and a collection rate, estimates the hazard and collection rate that best fit observed cohort repayment, and shows how portfolio growth flatters the portfolio collection rate.</t>
+          <t>Draws the expected repayment curve of a cohort from a monthly default hazard and a collection rate, estimates the hazard and collection rate that fit observed cohort repayment most closely, and shows how portfolio growth flatters the portfolio collection rate.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Read the best fitting hazard and collection rate, and compare the fitted curve with the observations.</t>
+          <t>Read the closest fitting hazard and collection rate, and compare the fitted curve with the observations.</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Links to the Volume 2 model and book</t>
+          <t>Links to Book 2 and MODEL 2</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -956,7 +956,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D3&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D3 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -986,7 +986,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1025,7 +1025,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D3  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D3  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -2129,7 +2129,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D3&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D3 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2177,7 +2177,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2267,7 +2267,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D3  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D3  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Best fit</t>
+          <t>Closest fit</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="12">
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Collection rate</t>
+          <t>Collection rate on paying accounts</t>
         </is>
       </c>
       <c r="F12" s="21">
@@ -15364,7 +15364,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D3&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D3 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15396,7 +15396,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15441,7 +15441,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D3  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D3  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -15489,7 +15489,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Portfolio collection rate in a steady growth state</t>
+          <t>Portfolio operational collection rate (not a PERFORM KPI), steady growth state</t>
         </is>
       </c>
       <c r="B9" s="21">
@@ -17074,7 +17074,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D3&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D3 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
